--- a/服装档口管理模板_v4.xlsx
+++ b/服装档口管理模板_v4.xlsx
@@ -890,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1038,6 +1038,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="32" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="32" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3094,7 +3103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4355,6 +4364,427 @@
         <v>4</v>
       </c>
       <c r="Q23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>内衣</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E24" s="55" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="G24" s="55" t="inlineStr">
+        <is>
+          <t>A架-3层</t>
+        </is>
+      </c>
+      <c r="H24" s="57" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I24" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="55" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr"/>
+      <c r="B25" s="55" t="inlineStr"/>
+      <c r="C25" s="55" t="inlineStr"/>
+      <c r="D25" s="56" t="inlineStr"/>
+      <c r="E25" s="55" t="inlineStr"/>
+      <c r="F25" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="G25" s="55" t="inlineStr"/>
+      <c r="H25" s="57" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I25" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="55" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="inlineStr"/>
+      <c r="B26" s="55" t="inlineStr"/>
+      <c r="C26" s="55" t="inlineStr"/>
+      <c r="D26" s="56" t="inlineStr"/>
+      <c r="E26" s="55" t="inlineStr"/>
+      <c r="F26" s="55" t="inlineStr">
+        <is>
+          <t>粉</t>
+        </is>
+      </c>
+      <c r="G26" s="55" t="inlineStr"/>
+      <c r="H26" s="57" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I26" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="55" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr"/>
+      <c r="B27" s="55" t="inlineStr"/>
+      <c r="C27" s="55" t="inlineStr"/>
+      <c r="D27" s="56" t="inlineStr"/>
+      <c r="E27" s="55" t="inlineStr"/>
+      <c r="F27" s="55" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="G27" s="55" t="inlineStr"/>
+      <c r="H27" s="57" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I27" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="55" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>UN-008</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>内裤</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>beyond</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E28" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F28" s="55" t="inlineStr">
+        <is>
+          <t>灰</t>
+        </is>
+      </c>
+      <c r="G28" s="55" t="inlineStr">
+        <is>
+          <t>B架-4层</t>
+        </is>
+      </c>
+      <c r="H28" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="54" t="n">
+        <v>20</v>
+      </c>
+      <c r="M28" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="N28" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="P28" s="54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q28" s="55" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="inlineStr"/>
+      <c r="B29" s="55" t="inlineStr"/>
+      <c r="C29" s="55" t="inlineStr"/>
+      <c r="D29" s="56" t="inlineStr"/>
+      <c r="E29" s="55" t="inlineStr"/>
+      <c r="F29" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="G29" s="55" t="inlineStr"/>
+      <c r="H29" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q29" s="55" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr"/>
+      <c r="B30" s="55" t="inlineStr"/>
+      <c r="C30" s="55" t="inlineStr"/>
+      <c r="D30" s="56" t="inlineStr"/>
+      <c r="E30" s="55" t="inlineStr"/>
+      <c r="F30" s="55" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="G30" s="55" t="inlineStr"/>
+      <c r="H30" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M30" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q30" s="55" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="55" t="inlineStr"/>
+      <c r="B31" s="55" t="inlineStr"/>
+      <c r="C31" s="55" t="inlineStr"/>
+      <c r="D31" s="56" t="inlineStr"/>
+      <c r="E31" s="55" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F31" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="G31" s="55" t="inlineStr"/>
+      <c r="H31" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" s="54" t="n">
+        <v>20</v>
+      </c>
+      <c r="M31" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="P31" s="54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q31" s="55" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr"/>
+      <c r="B32" s="55" t="inlineStr"/>
+      <c r="C32" s="55" t="inlineStr"/>
+      <c r="D32" s="56" t="inlineStr"/>
+      <c r="E32" s="55" t="inlineStr"/>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>灰</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr"/>
+      <c r="H32" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="N32" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q32" s="55" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -4416,7 +4846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5528,6 +5958,355 @@
       <c r="M23" s="4">
         <f>IF(J23&lt;=0,"缺货",IF(J23&lt;K23,"不足","充足"))</f>
         <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>内衣</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D24" s="55" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E24" s="55" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="G24" s="55" t="inlineStr">
+        <is>
+          <t>A架-3层</t>
+        </is>
+      </c>
+      <c r="H24" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>充足</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr"/>
+      <c r="B25" s="55" t="inlineStr"/>
+      <c r="C25" s="55" t="inlineStr"/>
+      <c r="D25" s="55" t="inlineStr"/>
+      <c r="E25" s="55" t="inlineStr"/>
+      <c r="F25" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="G25" s="55" t="inlineStr"/>
+      <c r="H25" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="inlineStr"/>
+      <c r="B26" s="55" t="inlineStr"/>
+      <c r="C26" s="55" t="inlineStr"/>
+      <c r="D26" s="55" t="inlineStr"/>
+      <c r="E26" s="55" t="inlineStr"/>
+      <c r="F26" s="55" t="inlineStr">
+        <is>
+          <t>粉</t>
+        </is>
+      </c>
+      <c r="G26" s="55" t="inlineStr"/>
+      <c r="H26" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" s="55" t="inlineStr">
+        <is>
+          <t>不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr"/>
+      <c r="B27" s="55" t="inlineStr"/>
+      <c r="C27" s="55" t="inlineStr"/>
+      <c r="D27" s="55" t="inlineStr"/>
+      <c r="E27" s="55" t="inlineStr"/>
+      <c r="F27" s="55" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="G27" s="55" t="inlineStr"/>
+      <c r="H27" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" s="55" t="inlineStr">
+        <is>
+          <t>不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>UN-008</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>内裤</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>beyond</t>
+        </is>
+      </c>
+      <c r="D28" s="55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E28" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F28" s="55" t="inlineStr">
+        <is>
+          <t>灰</t>
+        </is>
+      </c>
+      <c r="G28" s="55" t="inlineStr">
+        <is>
+          <t>B架-4层</t>
+        </is>
+      </c>
+      <c r="H28" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="K28" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="55" t="inlineStr">
+        <is>
+          <t>充足</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="inlineStr"/>
+      <c r="B29" s="55" t="inlineStr"/>
+      <c r="C29" s="55" t="inlineStr"/>
+      <c r="D29" s="55" t="inlineStr"/>
+      <c r="E29" s="55" t="inlineStr"/>
+      <c r="F29" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="G29" s="55" t="inlineStr"/>
+      <c r="H29" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" s="55" t="inlineStr">
+        <is>
+          <t>不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr"/>
+      <c r="B30" s="55" t="inlineStr"/>
+      <c r="C30" s="55" t="inlineStr"/>
+      <c r="D30" s="55" t="inlineStr"/>
+      <c r="E30" s="55" t="inlineStr"/>
+      <c r="F30" s="55" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="G30" s="55" t="inlineStr"/>
+      <c r="H30" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="55" t="inlineStr">
+        <is>
+          <t>充足</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="55" t="inlineStr"/>
+      <c r="B31" s="55" t="inlineStr"/>
+      <c r="C31" s="55" t="inlineStr"/>
+      <c r="D31" s="55" t="inlineStr"/>
+      <c r="E31" s="55" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F31" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="G31" s="55" t="inlineStr"/>
+      <c r="H31" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="K31" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="55" t="inlineStr">
+        <is>
+          <t>充足</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr"/>
+      <c r="B32" s="55" t="inlineStr"/>
+      <c r="C32" s="55" t="inlineStr"/>
+      <c r="D32" s="55" t="inlineStr"/>
+      <c r="E32" s="55" t="inlineStr"/>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>灰</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr"/>
+      <c r="H32" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="55" t="inlineStr">
+        <is>
+          <t>充足</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5603,7 +6382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -6875,6 +7654,474 @@
         <v/>
       </c>
       <c r="L26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>PI-1023</t>
+        </is>
+      </c>
+      <c r="C27" s="55" t="inlineStr">
+        <is>
+          <t>华为 批发</t>
+        </is>
+      </c>
+      <c r="D27" s="55" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="E27" s="55" t="inlineStr">
+        <is>
+          <t>内衣</t>
+        </is>
+      </c>
+      <c r="F27" s="55" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="G27" s="55" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="H27" s="55" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I27" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="55" t="n">
+        <v>25</v>
+      </c>
+      <c r="L27" s="55" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>PI-1024</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>华为 批发</t>
+        </is>
+      </c>
+      <c r="D28" s="55" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="E28" s="55" t="inlineStr">
+        <is>
+          <t>内衣</t>
+        </is>
+      </c>
+      <c r="F28" s="55" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="G28" s="55" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="H28" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="I28" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="55" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t>PI-1025</t>
+        </is>
+      </c>
+      <c r="C29" s="55" t="inlineStr">
+        <is>
+          <t>华为 批发</t>
+        </is>
+      </c>
+      <c r="D29" s="55" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="E29" s="55" t="inlineStr">
+        <is>
+          <t>内衣</t>
+        </is>
+      </c>
+      <c r="F29" s="55" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="G29" s="55" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="H29" s="55" t="inlineStr">
+        <is>
+          <t>粉</t>
+        </is>
+      </c>
+      <c r="I29" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" s="55" t="n">
+        <v>15</v>
+      </c>
+      <c r="L29" s="55" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>PI-1026</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>华为 批发</t>
+        </is>
+      </c>
+      <c r="D30" s="55" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="E30" s="55" t="inlineStr">
+        <is>
+          <t>内衣</t>
+        </is>
+      </c>
+      <c r="F30" s="55" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="G30" s="55" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="H30" s="55" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="I30" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" s="55" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>PI-1027</t>
+        </is>
+      </c>
+      <c r="C31" s="55" t="inlineStr">
+        <is>
+          <t>beyond 代理</t>
+        </is>
+      </c>
+      <c r="D31" s="55" t="inlineStr">
+        <is>
+          <t>UN-008</t>
+        </is>
+      </c>
+      <c r="E31" s="55" t="inlineStr">
+        <is>
+          <t>内裤</t>
+        </is>
+      </c>
+      <c r="F31" s="55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G31" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H31" s="55" t="inlineStr">
+        <is>
+          <t>灰</t>
+        </is>
+      </c>
+      <c r="I31" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="55" t="n">
+        <v>120</v>
+      </c>
+      <c r="L31" s="55" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>PI-1028</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>beyond 代理</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>UN-008</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>内裤</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H32" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="I32" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" s="55" t="n">
+        <v>30</v>
+      </c>
+      <c r="L32" s="55" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B33" s="55" t="inlineStr">
+        <is>
+          <t>PI-1029</t>
+        </is>
+      </c>
+      <c r="C33" s="55" t="inlineStr">
+        <is>
+          <t>beyond 代理</t>
+        </is>
+      </c>
+      <c r="D33" s="55" t="inlineStr">
+        <is>
+          <t>UN-008</t>
+        </is>
+      </c>
+      <c r="E33" s="55" t="inlineStr">
+        <is>
+          <t>内裤</t>
+        </is>
+      </c>
+      <c r="F33" s="55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G33" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H33" s="55" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="I33" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="L33" s="55" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t>PI-1030</t>
+        </is>
+      </c>
+      <c r="C34" s="55" t="inlineStr">
+        <is>
+          <t>beyond 代理</t>
+        </is>
+      </c>
+      <c r="D34" s="55" t="inlineStr">
+        <is>
+          <t>UN-008</t>
+        </is>
+      </c>
+      <c r="E34" s="55" t="inlineStr">
+        <is>
+          <t>内裤</t>
+        </is>
+      </c>
+      <c r="F34" s="55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G34" s="55" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="H34" s="55" t="inlineStr">
+        <is>
+          <t>肉</t>
+        </is>
+      </c>
+      <c r="I34" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="55" t="n">
+        <v>120</v>
+      </c>
+      <c r="L34" s="55" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="55" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B35" s="55" t="inlineStr">
+        <is>
+          <t>PI-1031</t>
+        </is>
+      </c>
+      <c r="C35" s="55" t="inlineStr">
+        <is>
+          <t>beyond 代理</t>
+        </is>
+      </c>
+      <c r="D35" s="55" t="inlineStr">
+        <is>
+          <t>UN-008</t>
+        </is>
+      </c>
+      <c r="E35" s="55" t="inlineStr">
+        <is>
+          <t>内裤</t>
+        </is>
+      </c>
+      <c r="F35" s="55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G35" s="55" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="H35" s="55" t="inlineStr">
+        <is>
+          <t>灰</t>
+        </is>
+      </c>
+      <c r="I35" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="L35" s="55" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
